--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54542.0</t>
+          <t>51617.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>45.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.89</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>91.67999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>101.91</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>111.26</t>
+          <t>111.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>99.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-136.04</t>
+          <t>-137.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5233790.0</t>
+          <t>4984403.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2309731.0</t>
+          <t>2820754.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1844425.0</t>
+          <t>2261178.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3953879.86</t>
+          <t>3861738.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>465306</t>
+          <t>559575</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-198733.5113556983</t>
+          <t>-121473.3345341895</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>121248.97</v>
+        <v>303457.64</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22862.0</t>
+          <t>54542.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-12.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>12.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>102.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>111.41</t>
+          <t>111.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>98.04</t>
+          <t>98.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.21</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-133.50</t>
+          <t>-136.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2099714.0</t>
+          <t>5233790.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1773950.4</t>
+          <t>2309731.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1403575.1</t>
+          <t>1844425.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3935122.22</t>
+          <t>3953879.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>370375</t>
+          <t>465306</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-256912.1438544184</t>
+          <t>-198733.5113556983</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-170099.49</v>
+        <v>121248.97</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9275.0</t>
+          <t>22862.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.69</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-12.01</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>104.68</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.71</t>
+          <t>111.41</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>97.57</t>
+          <t>98.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-62.93</t>
+          <t>-46.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.63</t>
+          <t>-133.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>812501.0</t>
+          <t>2099714.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1576176.0</t>
+          <t>1773950.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1341970.8</t>
+          <t>1403575.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4059655.58</t>
+          <t>3935122.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>234205</t>
+          <t>370375</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-272696.2628382232</t>
+          <t>-256912.1438544184</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-244442.73</v>
+        <v>-170099.49</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,112 +5634,112 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>93.36</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,55 +5830,55 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>14942.8</t>
+          <t>23481.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>17526.18</t>
+          <t>18406.26</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-972.64</v>
+        <v>1881.97</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,42 +5918,42 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6100,77 +6100,77 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,51 +6261,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>14844.8</t>
+          <t>14942.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>17368.58</t>
+          <t>17526.18</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-1257.89</v>
+        <v>-972.64</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,27 +6349,27 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6531,77 +6531,77 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,72 +6612,72 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6692,51 +6692,51 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>14098.8</t>
+          <t>14844.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>17251.7</t>
+          <t>17368.58</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-1380.99</v>
+        <v>-1257.89</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,42 +6780,42 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6962,49 +6962,49 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>2.27</t>
@@ -7012,27 +7012,27 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,42 +7058,42 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.53999999999999</t>
+          <t>94.05999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,51 +7123,51 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.59</t>
+          <t>-88.07</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16777.0</t>
+          <t>16437.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>12573.8</t>
+          <t>14098.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>13982.9</t>
+          <t>14361.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>17000.58</t>
+          <t>17251.7</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1409</t>
+          <t>-262</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-791.8796930297235</t>
+          <t>-882.5122878384688</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-1674.14</v>
+        <v>-1380.99</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7211,27 +7211,27 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7393,49 +7393,49 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>2.27</t>
@@ -7443,27 +7443,27 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>93.53999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,51 +7554,51 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-89.12</t>
+          <t>-88.59</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9501.0</t>
+          <t>16777.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12476.2</t>
+          <t>12573.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>13522.7</t>
+          <t>13982.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>16963.16</t>
+          <t>17000.58</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1409</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-631.4688097694574</t>
+          <t>-791.8796930297235</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-2069.56</v>
+        <v>-1674.14</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7642,27 +7642,27 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7824,77 +7824,77 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,142 +7905,142 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>92.86</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>90.94</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>89.78</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>16.86</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-89.12</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>113769.6264450867</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>9501.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12476.2</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>13522.7</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>16963.16</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-1046</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-631.4688097694574</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>-2069.56</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
         <is>
           <t>92.3</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>90.61</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>89.64</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>90.27</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-89.58</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>113820.974674385</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>16627.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>14186.4</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>14472.5</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>17076.44</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-286</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-369.9976352928859</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>-1780.96</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
       <c r="BF18" t="inlineStr">
         <is>
           <t>2025/10/30</t>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,27 +8073,27 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8163,17 +8163,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,112 +8220,112 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-7.76</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
           <t>34.21</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.64</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,51 +8416,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>-89.58</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11152.0</t>
+          <t>16627.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>14666.0</t>
+          <t>14186.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>15899.8</t>
+          <t>14472.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>16952.38</t>
+          <t>17076.44</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1233</t>
+          <t>-286</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-113.458529951833</t>
+          <t>-369.9976352928859</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-2068.57</v>
+        <v>-1780.96</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,42 +8504,42 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,22 +8661,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-31.70</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8686,77 +8686,77 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>92.62</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.25</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,55 +8847,55 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-90.16</t>
+          <t>-89.85</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>8812.0</t>
+          <t>11152.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>14623.2</t>
+          <t>14666.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>21411.2</t>
+          <t>15899.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>16837.82</t>
+          <t>16952.38</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-6788</t>
+          <t>-1233</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>242.017134129503</t>
+          <t>-113.458529951833</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-1818.96</v>
+        <v>-2068.57</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,22 +8935,22 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
@@ -8960,17 +8960,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-40.57</t>
+          <t>-31.70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9117,49 +9117,49 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>0</t>
@@ -9167,27 +9167,27 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.62</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,51 +9278,51 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-90.62</t>
+          <t>-90.16</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16289.0</t>
+          <t>8812.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>15392.0</t>
+          <t>14623.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>25898.3</t>
+          <t>21411.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>16802.94</t>
+          <t>16837.82</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-10506</t>
+          <t>-6788</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>616.7409970491414</t>
+          <t>242.017134129503</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-1146.7</v>
+        <v>-1818.96</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,27 +9366,27 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-48.50</t>
+          <t>-40.57</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9548,49 +9548,49 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
           <t>0</t>
@@ -9598,43 +9598,43 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.32000000000001</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,51 +9709,51 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-91.35</t>
+          <t>-90.62</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>18052.0</t>
+          <t>16289.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>14569.2</t>
+          <t>15392.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>28289.0</t>
+          <t>25898.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>17197.4</t>
+          <t>16802.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-13719</t>
+          <t>-10506</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>937.3666861440684</t>
+          <t>616.7409970491414</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-946.48</v>
+        <v>-1146.7</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,22 +9797,22 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-46.12</t>
+          <t>-48.50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9979,49 +9979,49 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>2025-11-14 00:00:00</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2024-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
           <t>0</t>
@@ -10029,27 +10029,27 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>-48.78</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,57 +10060,57 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>544</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>79.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>93.32000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -10120,17 +10120,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>101.79</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,51 +10140,51 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-92.64</t>
+          <t>-91.35</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>113820.974674385</t>
+          <t>113769.6264450867</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>19025.0</t>
+          <t>18052.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14758.6</t>
+          <t>14569.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27389.1</t>
+          <t>28289.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>17073.8</t>
+          <t>17197.4</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-12630</t>
+          <t>-13719</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1279.883714482261</t>
+          <t>937.3666861440684</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-815.53</v>
+        <v>-946.48</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>2.12480574261822</t>
+          <t>8.143300034447124</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-17.77135579207663</t>
+          <t>-10.93170756310998</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>6.706459576861777</t>
+          <t>1.439593030005594</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,162 +1024,162 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>1188956.751082251</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-233639.39</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1188212.132947977</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,29 +3412,29 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54542.0</t>
+          <t>51617.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>45.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.04</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.89</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>91.67999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>101.91</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>111.26</t>
+          <t>111.08</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>99.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-136.04</t>
+          <t>-137.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5233790.0</t>
+          <t>4984403.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2309731.0</t>
+          <t>2820754.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1844425.0</t>
+          <t>2261178.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3953879.86</t>
+          <t>3861738.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>465306</t>
+          <t>559575</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-198733.5113556983</t>
+          <t>-121473.3345341895</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>121248.97</v>
+        <v>303457.64</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22862.0</t>
+          <t>54542.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-12.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>12.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>102.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.41</t>
+          <t>111.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>98.04</t>
+          <t>98.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.21</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-133.50</t>
+          <t>-136.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2099714.0</t>
+          <t>5233790.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1773950.4</t>
+          <t>2309731.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1403575.1</t>
+          <t>1844425.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3935122.22</t>
+          <t>3953879.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>370375</t>
+          <t>465306</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-256912.1438544184</t>
+          <t>-198733.5113556983</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-170099.49</v>
+        <v>121248.97</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,74 +5634,74 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -5714,14 +5714,14 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>93.36</t>
+          <t>93.53</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23481.0</t>
+          <t>26929.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>18406.26</t>
+          <t>18957.08</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1881.97</v>
+        <v>2470.17</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,92 +6065,92 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-5.46</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3.73</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>93.36</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>14942.8</t>
+          <t>23481.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>17526.18</t>
+          <t>18406.26</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-972.64</v>
+        <v>1881.97</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>14844.8</t>
+          <t>14942.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>17368.58</t>
+          <t>17526.18</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-1257.89</v>
+        <v>-972.64</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,72 +7043,72 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>14098.8</t>
+          <t>14844.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>17251.7</t>
+          <t>17368.58</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-1380.99</v>
+        <v>-1257.89</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,42 +7489,42 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.53999999999999</t>
+          <t>94.05999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.59</t>
+          <t>-88.07</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16777.0</t>
+          <t>16437.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12573.8</t>
+          <t>14098.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>13982.9</t>
+          <t>14361.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>17000.58</t>
+          <t>17251.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1409</t>
+          <t>-262</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-791.8796930297235</t>
+          <t>-882.5122878384688</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-1674.14</v>
+        <v>-1380.99</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>93.53999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-89.12</t>
+          <t>-88.59</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9501.0</t>
+          <t>16777.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12476.2</t>
+          <t>12573.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13522.7</t>
+          <t>13982.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>16963.16</t>
+          <t>17000.58</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1409</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-631.4688097694574</t>
+          <t>-791.8796930297235</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-2069.56</v>
+        <v>-1674.14</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,142 +8336,142 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>92.86</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>90.94</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>89.78</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>16.86</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-89.12</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>113679.0909090909</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>9501.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12476.2</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>13522.7</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>16963.16</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-1046</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-631.4688097694574</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>-2069.56</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
         <is>
           <t>92.3</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>90.61</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>89.64</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>90.27</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-89.58</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>113769.6264450867</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>16627.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>14186.4</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>14472.5</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>17076.44</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-286</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-369.9976352928859</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>-1780.96</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>2025/10/30</t>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,79 +8651,79 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-7.76</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>34.21</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.64</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>-89.58</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>11152.0</t>
+          <t>16627.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>14666.0</t>
+          <t>14186.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>15899.8</t>
+          <t>14472.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>16952.38</t>
+          <t>17076.44</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1233</t>
+          <t>-286</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-113.458529951833</t>
+          <t>-369.9976352928859</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-2068.57</v>
+        <v>-1780.96</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,22 +9092,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-31.70</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>92.62</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.25</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-90.16</t>
+          <t>-89.85</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,45 +9288,45 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8812.0</t>
+          <t>11152.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>14623.2</t>
+          <t>14666.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>21411.2</t>
+          <t>15899.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>16837.82</t>
+          <t>16952.38</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-6788</t>
+          <t>-1233</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>242.017134129503</t>
+          <t>-113.458529951833</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-1818.96</v>
+        <v>-2068.57</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-40.57</t>
+          <t>-31.70</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.62</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-90.62</t>
+          <t>-90.16</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16289.0</t>
+          <t>8812.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>15392.0</t>
+          <t>14623.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>25898.3</t>
+          <t>21411.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>16802.94</t>
+          <t>16837.82</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-10506</t>
+          <t>-6788</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>616.7409970491414</t>
+          <t>242.017134129503</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-1146.7</v>
+        <v>-1818.96</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-48.50</t>
+          <t>-40.57</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,33 +10039,33 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.32000000000001</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-91.35</t>
+          <t>-90.62</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>113769.6264450867</t>
+          <t>113679.0909090909</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>18052.0</t>
+          <t>16289.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14569.2</t>
+          <t>15392.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>28289.0</t>
+          <t>25898.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>17197.4</t>
+          <t>16802.94</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-13719</t>
+          <t>-10506</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>937.3666861440684</t>
+          <t>616.7409970491414</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-946.48</v>
+        <v>-1146.7</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-233639.39</v>
+        <v>-260559.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,162 +1455,162 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1188385.067723343</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-233639.39</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1188956.751082251</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-9.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-9.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-13.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54542.0</t>
+          <t>51617.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-15.29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>45.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.89</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>91.67999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>101.91</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.26</t>
+          <t>111.08</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>99.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-136.04</t>
+          <t>-137.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5233790.0</t>
+          <t>4984403.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2309731.0</t>
+          <t>2820754.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1844425.0</t>
+          <t>2261178.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3953879.86</t>
+          <t>3861738.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>465306</t>
+          <t>559575</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-198733.5113556983</t>
+          <t>-121473.3345341895</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>121248.97</v>
+        <v>303457.64</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,72 +5634,72 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>93.53</t>
+          <t>93.46</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-88.85</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>26929.4</t>
+          <t>27481.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>19751.6</t>
+          <t>20789.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>18957.08</t>
+          <t>19031.22</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-51.75580132153277</t>
+          <t>219.0315246548028</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2470.17</v>
+        <v>1708.36</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,74 +6065,74 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-5.46</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -6145,14 +6145,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.36</t>
+          <t>93.53</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>23481.0</t>
+          <t>26929.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>18406.26</t>
+          <t>18957.08</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>1881.97</v>
+        <v>2470.17</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,92 +6496,92 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>93.36</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>14942.8</t>
+          <t>23481.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>17526.18</t>
+          <t>18406.26</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-972.64</v>
+        <v>1881.97</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>14844.8</t>
+          <t>14942.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>17368.58</t>
+          <t>17526.18</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-1257.89</v>
+        <v>-972.64</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,72 +7474,72 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>14098.8</t>
+          <t>14844.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>17251.7</t>
+          <t>17368.58</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-1380.99</v>
+        <v>-1257.89</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,42 +7920,42 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.53999999999999</t>
+          <t>94.05999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.59</t>
+          <t>-88.07</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16777.0</t>
+          <t>16437.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12573.8</t>
+          <t>14098.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13982.9</t>
+          <t>14361.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>17000.58</t>
+          <t>17251.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1409</t>
+          <t>-262</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-791.8796930297235</t>
+          <t>-882.5122878384688</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-1674.14</v>
+        <v>-1380.99</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>93.53999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-89.12</t>
+          <t>-88.59</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9501.0</t>
+          <t>16777.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12476.2</t>
+          <t>12573.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13522.7</t>
+          <t>13982.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>16963.16</t>
+          <t>17000.58</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1409</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-631.4688097694574</t>
+          <t>-791.8796930297235</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-2069.56</v>
+        <v>-1674.14</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,142 +8767,142 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>92.86</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>90.94</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>89.78</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>16.86</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-89.12</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>113556.7759365994</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>9501.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>12476.2</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>13522.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>16963.16</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-1046</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-631.4688097694574</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>-2069.56</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
         <is>
           <t>92.3</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>90.61</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>89.64</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>90.27</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-89.58</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>113679.0909090909</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>16627.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>14186.4</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>14472.5</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>17076.44</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>-286</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-369.9976352928859</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>-1780.96</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
       <c r="BF20" t="inlineStr">
         <is>
           <t>2025/10/30</t>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9025,17 +9025,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,79 +9082,79 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-7.76</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
           <t>34.21</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.64</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>-89.58</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11152.0</t>
+          <t>16627.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>14666.0</t>
+          <t>14186.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15899.8</t>
+          <t>14472.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>16952.38</t>
+          <t>17076.44</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1233</t>
+          <t>-286</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-113.458529951833</t>
+          <t>-369.9976352928859</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-2068.57</v>
+        <v>-1780.96</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,22 +9523,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-31.70</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>92.62</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.25</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-90.16</t>
+          <t>-89.85</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8812.0</t>
+          <t>11152.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>14623.2</t>
+          <t>14666.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>21411.2</t>
+          <t>15899.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>16837.82</t>
+          <t>16952.38</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-6788</t>
+          <t>-1233</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>242.017134129503</t>
+          <t>-113.458529951833</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-1818.96</v>
+        <v>-2068.57</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-40.57</t>
+          <t>-31.70</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.62</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-90.62</t>
+          <t>-90.16</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>113679.0909090909</t>
+          <t>113556.7759365994</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16289.0</t>
+          <t>8812.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>15392.0</t>
+          <t>14623.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>25898.3</t>
+          <t>21411.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>16802.94</t>
+          <t>16837.82</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-10506</t>
+          <t>-6788</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>616.7409970491414</t>
+          <t>242.017134129503</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-1146.7</v>
+        <v>-1818.96</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-260559.83</v>
+        <v>-276461.79</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-233639.39</v>
+        <v>-260559.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,162 +1886,162 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1187712.248201439</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-233639.39</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1188385.067723343</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,62 +2515,62 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
+          <t>92.04</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>15.18%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>-2.36%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>85.54</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>33468</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>中光電-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>84.12</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>32725</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-9.56</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-13.74</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-15.29</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -5755,72 +5755,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>93.05999999999999</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>93.46</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-21.66</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-89.27</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27481.0</t>
+          <t>29946.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20789.9</t>
+          <t>22395.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>19031.22</t>
+          <t>19406.42</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>219.0315246548028</t>
+          <t>452.0397351167907</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1708.36</v>
+        <v>1733.58</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6008,17 +6008,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,72 +6065,72 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,72 +6186,72 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.53</t>
+          <t>93.46</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-88.85</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26929.4</t>
+          <t>27481.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>19751.6</t>
+          <t>20789.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>18957.08</t>
+          <t>19031.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-51.75580132153277</t>
+          <t>219.0315246548028</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>2470.17</v>
+        <v>1708.36</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,74 +6496,74 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -6576,14 +6576,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,72 +6617,72 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>93.36</t>
+          <t>93.53</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>23481.0</t>
+          <t>26929.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>18406.26</t>
+          <t>18957.08</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>1881.97</v>
+        <v>2470.17</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,92 +6927,92 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,72 +7048,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>93.36</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>14942.8</t>
+          <t>23481.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>17526.18</t>
+          <t>18406.26</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-972.64</v>
+        <v>1881.97</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,72 +7479,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>14844.8</t>
+          <t>14942.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>17368.58</t>
+          <t>17526.18</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-1257.89</v>
+        <v>-972.64</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,67 +7910,67 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>14098.8</t>
+          <t>14844.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>17251.7</t>
+          <t>17368.58</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-1380.99</v>
+        <v>-1257.89</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,42 +8351,42 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.53999999999999</t>
+          <t>94.05999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.59</t>
+          <t>-88.07</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>16777.0</t>
+          <t>16437.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12573.8</t>
+          <t>14098.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13982.9</t>
+          <t>14361.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>17000.58</t>
+          <t>17251.7</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1409</t>
+          <t>-262</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-791.8796930297235</t>
+          <t>-882.5122878384688</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-1674.14</v>
+        <v>-1380.99</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>93.53999999999999</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-89.12</t>
+          <t>-88.59</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>9501.0</t>
+          <t>16777.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>12476.2</t>
+          <t>12573.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13522.7</t>
+          <t>13982.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>16963.16</t>
+          <t>17000.58</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1409</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-631.4688097694574</t>
+          <t>-791.8796930297235</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-2069.56</v>
+        <v>-1674.14</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,17 +9020,17 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,137 +9203,137 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>92.86</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>90.94</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>89.78</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>16.86</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-89.12</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>113452.1136690647</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>9501.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>12476.2</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>13522.7</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>16963.16</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-1046</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-631.4688097694574</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-2069.56</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
         <is>
           <t>92.3</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>90.61</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>89.64</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>90.27</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-89.58</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>113556.7759365994</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>16627.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>14186.4</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>14472.5</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>17076.44</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-286</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-369.9976352928859</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-1780.96</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
       <c r="BF21" t="inlineStr">
         <is>
           <t>2025/10/30</t>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9456,17 +9456,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,79 +9513,79 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-7.76</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>92.7</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,72 +9634,72 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
           <t>34.21</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.64</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>-89.58</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11152.0</t>
+          <t>16627.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>14666.0</t>
+          <t>14186.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>15899.8</t>
+          <t>14472.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>16952.38</t>
+          <t>17076.44</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1233</t>
+          <t>-286</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-113.458529951833</t>
+          <t>-369.9976352928859</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-2068.57</v>
+        <v>-1780.96</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,22 +9954,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-31.70</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,72 +10065,72 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>92.62</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.25</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-90.16</t>
+          <t>-89.85</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,45 +10150,45 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>113556.7759365994</t>
+          <t>113452.1136690647</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8812.0</t>
+          <t>11152.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14623.2</t>
+          <t>14666.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>21411.2</t>
+          <t>15899.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>16837.82</t>
+          <t>16952.38</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-6788</t>
+          <t>-1233</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>242.017134129503</t>
+          <t>-113.458529951833</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-1818.96</v>
+        <v>-2068.57</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>676255.8</t>
+          <t>797567.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2237649.02</t>
+          <t>2222751.52</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>446832</v>
+        <v>1396196</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,24 +1272,24 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>85.1</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>810164.4</t>
+          <t>676255.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2333587.64</t>
+          <t>2237649.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>480517</v>
+        <v>446832</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>528139</v>
+        <v>480517</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1136155</v>
+        <v>528139</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,167 +2773,167 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1188270.522955524</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-233639.3877835108</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>1136155</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1186968.765086207</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-251981.9240553796</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>789636</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1116375</v>
+        <v>789636</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>702772</v>
+        <v>1116375</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>914371</v>
+        <v>702772</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-113090.384887269</t>
+          <t>-175290.3456510033</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1185679</v>
+        <v>914371</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-49263.07005024608</t>
+          <t>-113090.384887269</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1068845</v>
+        <v>1185679</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,24 +5196,24 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
       <c r="CH11" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>56196.13221872458</t>
+          <t>-49263.07005024608</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1291202</v>
+        <v>1068845</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,17 +5810,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5850,37 +5850,37 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>93.32</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>93.34</t>
+          <t>93.21</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-26.15</t>
+          <t>-35.13</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-89.93</t>
+          <t>-90.74</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>29288.8</t>
+          <t>21669.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>22115.8</t>
+          <t>22575.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>19553.94</t>
+          <t>19566.56</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>-905</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>490.8184563195054</t>
+          <t>413.1595335864695</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>704.1014229344364</t>
+          <t>-13.96454144522795</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>13827</v>
+        <v>14096</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,98 +6225,98 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.32</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>93.34</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-26.15</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-89.27</t>
+          <t>-89.93</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29946.8</t>
+          <t>29288.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>22395.8</t>
+          <t>22115.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>19406.42</t>
+          <t>19553.94</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>452.0397351167907</t>
+          <t>490.8184563195054</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1733.584892657724</t>
+          <t>704.1014229344364</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>27211</v>
+        <v>13827</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,98 +6661,98 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.05999999999999</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>93.46</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-21.66</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-89.27</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>27481.0</t>
+          <t>29946.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>20789.9</t>
+          <t>22395.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>19031.22</t>
+          <t>19406.42</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>219.0315246548028</t>
+          <t>452.0397351167907</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1708.361817524648</t>
+          <t>1733.584892657724</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>19195</v>
+        <v>27211</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6945,17 +6945,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,72 +7002,72 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>93.53</t>
+          <t>93.46</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-88.85</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>26929.4</t>
+          <t>27481.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>19751.6</t>
+          <t>20789.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>18957.08</t>
+          <t>19031.22</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-51.75580132153277</t>
+          <t>219.0315246548028</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2470.173073851518</t>
+          <t>1708.361817524648</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>34019</v>
+        <v>19195</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,74 +7438,74 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-4.89</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>93.36</t>
+          <t>93.53</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>23481.0</t>
+          <t>26929.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>18406.26</t>
+          <t>18957.08</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1881.968687395205</t>
+          <t>2470.173073851518</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>52192</v>
+        <v>34019</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,92 +7874,92 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>93.36</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>14942.8</t>
+          <t>23481.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>17526.18</t>
+          <t>18406.26</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-972.6436035207844</t>
+          <t>1881.968687395205</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>17117</v>
+        <v>52192</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>14844.8</t>
+          <t>14942.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>17368.58</t>
+          <t>17526.18</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1257.888176132168</t>
+          <t>-972.6436035207844</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>14882</v>
+        <v>17117</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,72 +8862,72 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>14098.8</t>
+          <t>14844.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>17251.7</t>
+          <t>17368.58</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1380.991559286567</t>
+          <t>-1257.888176132168</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>16437</v>
+        <v>14882</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,42 +9313,42 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.53999999999999</t>
+          <t>94.05999999999999</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-88.59</t>
+          <t>-88.07</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16777.0</t>
+          <t>16437.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>12573.8</t>
+          <t>14098.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13982.9</t>
+          <t>14361.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>17000.58</t>
+          <t>17251.7</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1409</t>
+          <t>-262</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-791.8796930297235</t>
+          <t>-882.5122878384688</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1674.139550961187</t>
+          <t>-1380.991559286567</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>16777</v>
+        <v>16437</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>93.53999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-89.12</t>
+          <t>-88.59</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>113318.9073275862</t>
+          <t>113186.6621233859</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9501.0</t>
+          <t>16777.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12476.2</t>
+          <t>12573.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13522.7</t>
+          <t>13982.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>16963.16</t>
+          <t>17000.58</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1409</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-631.4688097694574</t>
+          <t>-791.8796930297235</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-2069.5602693906</t>
+          <t>-1674.139550961187</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>9501</v>
+        <v>16777</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,147 +10170,147 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>92.86</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>90.94</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>89.78</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>16.86</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-89.12</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>113186.6621233859</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>9501.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>12476.2</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>13522.7</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>16963.16</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-1046</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-631.4688097694574</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-2069.5602693906</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>9501</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
         <is>
           <t>92.3</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>90.61</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>89.64</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>90.27</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-89.58</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>113318.9073275862</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>16627.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>14186.4</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>14472.5</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>17076.44</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-286</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-369.9976352928859</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-1780.962714668676</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>16627</v>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
       <c r="BG23" t="inlineStr">
         <is>
           <t>2025/10/30</t>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10433,17 +10433,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>101.99</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>797567.8</t>
+          <t>993448.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2222751.52</t>
+          <t>2145653.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1396196</v>
+        <v>2115557</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>676255.8</t>
+          <t>797567.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2237649.02</t>
+          <t>2222751.52</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>446832</v>
+        <v>1396196</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>810164.4</t>
+          <t>676255.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2333587.64</t>
+          <t>2237649.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>480517</v>
+        <v>446832</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>528139</v>
+        <v>480517</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1136155</v>
+        <v>528139</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>941766.6</t>
+          <t>931861.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2858383.84</t>
+          <t>2699451.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>789636</v>
+        <v>1136155</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,27 +3447,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1116375</v>
+        <v>789636</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>702772</v>
+        <v>1116375</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,27 +4319,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>914371</v>
+        <v>702772</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-113090.384887269</t>
+          <t>-175290.3456510033</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1185679</v>
+        <v>914371</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-49263.07005024608</t>
+          <t>-113090.384887269</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1068845</v>
+        <v>1185679</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,37 +5810,37 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.14</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>93.21</t>
+          <t>93.08</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -5865,22 +5865,22 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-35.13</t>
+          <t>-57.38</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>21669.6</t>
+          <t>20304.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>22575.3</t>
+          <t>23617.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>19566.56</t>
+          <t>19939.46</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-905</t>
+          <t>-3312</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>413.1595335864695</t>
+          <t>421.3024356539564</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-13.96454144522795</t>
+          <t>466.0883970251343</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>14096</v>
+        <v>27194</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6286,37 +6286,37 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.32</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.34</t>
+          <t>93.21</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-26.15</t>
+          <t>-35.13</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-89.93</t>
+          <t>-90.74</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29288.8</t>
+          <t>21669.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>22115.8</t>
+          <t>22575.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>19553.94</t>
+          <t>19566.56</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>-905</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>490.8184563195054</t>
+          <t>413.1595335864695</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>704.1014229344364</t>
+          <t>-13.96454144522795</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>13827</v>
+        <v>14096</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,98 +6661,98 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.32</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>93.34</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-26.15</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-89.27</t>
+          <t>-89.93</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29946.8</t>
+          <t>29288.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>22395.8</t>
+          <t>22115.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>19406.42</t>
+          <t>19553.94</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>452.0397351167907</t>
+          <t>490.8184563195054</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1733.584892657724</t>
+          <t>704.1014229344364</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>27211</v>
+        <v>13827</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,98 +7097,98 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.05999999999999</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>93.46</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-21.66</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-89.27</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>27481.0</t>
+          <t>29946.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>20789.9</t>
+          <t>22395.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>19031.22</t>
+          <t>19406.42</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>219.0315246548028</t>
+          <t>452.0397351167907</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1708.361817524648</t>
+          <t>1733.584892657724</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>19195</v>
+        <v>27211</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7381,17 +7381,17 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,72 +7438,72 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>93.53</t>
+          <t>93.46</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-88.85</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>26929.4</t>
+          <t>27481.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>19751.6</t>
+          <t>20789.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>18957.08</t>
+          <t>19031.22</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-51.75580132153277</t>
+          <t>219.0315246548028</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2470.173073851518</t>
+          <t>1708.361817524648</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>34019</v>
+        <v>19195</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,74 +7874,74 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -7954,14 +7954,14 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>93.36</t>
+          <t>93.53</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23481.0</t>
+          <t>26929.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18406.26</t>
+          <t>18957.08</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1881.968687395205</t>
+          <t>2470.173073851518</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>52192</v>
+        <v>34019</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,92 +8310,92 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-6.98</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>93.36</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>14942.8</t>
+          <t>23481.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>17526.18</t>
+          <t>18406.26</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-972.6436035207844</t>
+          <t>1881.968687395205</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>17117</v>
+        <v>52192</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>14844.8</t>
+          <t>14942.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>17368.58</t>
+          <t>17526.18</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1257.888176132168</t>
+          <t>-972.6436035207844</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>14882</v>
+        <v>17117</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,72 +9298,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>14098.8</t>
+          <t>14844.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>17251.7</t>
+          <t>17368.58</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1380.991559286567</t>
+          <t>-1257.888176132168</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>16437</v>
+        <v>14882</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,42 +9749,42 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.53999999999999</t>
+          <t>94.05999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9794,17 +9794,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.59</t>
+          <t>-88.07</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16777.0</t>
+          <t>16437.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12573.8</t>
+          <t>14098.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13982.9</t>
+          <t>14361.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>17000.58</t>
+          <t>17251.7</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1409</t>
+          <t>-262</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-791.8796930297235</t>
+          <t>-882.5122878384688</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1674.139550961187</t>
+          <t>-1380.991559286567</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>16777</v>
+        <v>16437</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>301</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>93.53999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-89.12</t>
+          <t>-88.59</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>113186.6621233859</t>
+          <t>113082.9434097421</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9501.0</t>
+          <t>16777.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>12476.2</t>
+          <t>12573.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>13522.7</t>
+          <t>13982.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>16963.16</t>
+          <t>17000.58</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1409</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-631.4688097694574</t>
+          <t>-791.8796930297235</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-2069.5602693906</t>
+          <t>-1674.139550961187</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>9501</v>
+        <v>16777</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>101.99</t>
+          <t>101.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>993448.2</t>
+          <t>1187172.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2145653.4</t>
+          <t>2058125.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2115557</v>
+        <v>1496761</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>101.99</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>797567.8</t>
+          <t>993448.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2222751.52</t>
+          <t>2145653.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1396196</v>
+        <v>2115557</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>676255.8</t>
+          <t>797567.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2237649.02</t>
+          <t>2222751.52</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>446832</v>
+        <v>1396196</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,24 +2144,24 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>85.1</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
       <c r="CH4" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>810164.4</t>
+          <t>676255.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2333587.64</t>
+          <t>2237649.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>480517</v>
+        <v>446832</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>528139</v>
+        <v>480517</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1136155</v>
+        <v>528139</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>941766.6</t>
+          <t>931861.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2858383.84</t>
+          <t>2699451.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>789636</v>
+        <v>1136155</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1116375</v>
+        <v>789636</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>702772</v>
+        <v>1116375</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>914371</v>
+        <v>702772</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-113090.384887269</t>
+          <t>-175290.3456510033</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1185679</v>
+        <v>914371</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,62 +5825,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>92.14</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>93.08</t>
+          <t>92.84</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-57.38</t>
+          <t>-90.81</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>27194.0</t>
+          <t>34018.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20304.6</t>
+          <t>23269.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>23617.0</t>
+          <t>25375.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>19939.46</t>
+          <t>20196.08</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3312</t>
+          <t>-2105</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>421.3024356539564</t>
+          <t>556.8364061731578</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>466.0883970251343</t>
+          <t>1302.273244028765</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>27194</v>
+        <v>34018</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.14</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.21</t>
+          <t>93.08</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -6301,22 +6301,22 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-35.13</t>
+          <t>-57.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21669.6</t>
+          <t>20304.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>22575.3</t>
+          <t>23617.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>19566.56</t>
+          <t>19939.46</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-905</t>
+          <t>-3312</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>413.1595335864695</t>
+          <t>421.3024356539564</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-13.96454144522795</t>
+          <t>466.0883970251343</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>14096</v>
+        <v>27194</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,17 +6702,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6722,37 +6722,37 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.32</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>93.34</t>
+          <t>93.21</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-26.15</t>
+          <t>-35.13</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-89.93</t>
+          <t>-90.74</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29288.8</t>
+          <t>21669.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>22115.8</t>
+          <t>22575.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>19553.94</t>
+          <t>19566.56</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>-905</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>490.8184563195054</t>
+          <t>413.1595335864695</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>704.1014229344364</t>
+          <t>-13.96454144522795</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>13827</v>
+        <v>14096</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,22 +7097,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -7123,72 +7123,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.32</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>93.34</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-26.15</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-89.27</t>
+          <t>-89.93</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29946.8</t>
+          <t>29288.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22395.8</t>
+          <t>22115.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>19406.42</t>
+          <t>19553.94</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>452.0397351167907</t>
+          <t>490.8184563195054</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1733.584892657724</t>
+          <t>704.1014229344364</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>27211</v>
+        <v>13827</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-5.6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,22 +7533,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -7559,72 +7559,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.05999999999999</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>93.46</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-21.66</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-89.27</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27481.0</t>
+          <t>29946.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>20789.9</t>
+          <t>22395.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>19031.22</t>
+          <t>19406.42</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>219.0315246548028</t>
+          <t>452.0397351167907</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1708.361817524648</t>
+          <t>1733.584892657724</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>19195</v>
+        <v>27211</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,72 +7874,72 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-3.64</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-1.44</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,212 +7995,212 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>93.53</t>
+          <t>93.46</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-88.85</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>112994.1652360515</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>27481.0</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>20789.9</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>19031.22</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>6691</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>219.0315246548028</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>1708.361817524648</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>19195</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-88.25</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>113082.9434097421</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>34019.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>26929.4</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>19751.6</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>18957.08</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>7177</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-51.75580132153277</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>2470.173073851518</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>34019</v>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
       <c r="BU18" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,74 +8310,74 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-2.58</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-3.64</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-6.98</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -8390,14 +8390,14 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,72 +8431,72 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>93.36</t>
+          <t>93.53</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23481.0</t>
+          <t>26929.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>18406.26</t>
+          <t>18957.08</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1881.968687395205</t>
+          <t>2470.173073851518</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>52192</v>
+        <v>34019</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,92 +8746,92 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-8.17</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-3.64</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,72 +8867,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>93.36</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>14942.8</t>
+          <t>23481.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>17526.18</t>
+          <t>18406.26</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-972.6436035207844</t>
+          <t>1881.968687395205</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>17117</v>
+        <v>52192</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,72 +9303,72 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>14844.8</t>
+          <t>14942.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>17368.58</t>
+          <t>17526.18</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1257.888176132168</t>
+          <t>-972.6436035207844</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>14882</v>
+        <v>17117</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,67 +9739,67 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>14098.8</t>
+          <t>14844.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>17251.7</t>
+          <t>17368.58</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1380.991559286567</t>
+          <t>-1257.888176132168</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>16437</v>
+        <v>14882</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,42 +10185,42 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.53999999999999</t>
+          <t>94.05999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-88.59</t>
+          <t>-88.07</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>113082.9434097421</t>
+          <t>112994.1652360515</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16777.0</t>
+          <t>16437.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>12573.8</t>
+          <t>14098.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>13982.9</t>
+          <t>14361.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>17000.58</t>
+          <t>17251.7</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1409</t>
+          <t>-262</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-791.8796930297235</t>
+          <t>-882.5122878384688</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1674.139550961187</t>
+          <t>-1380.991559286567</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>16777</v>
+        <v>16437</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>88.82</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>101.54</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>101.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1496761.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1187172.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1187172.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1020894.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2058125.44</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2058125.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-65418.32762892707</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1496761</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1496761.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>85.55999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>89.42</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>101.99</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>101.99</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2115557.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>993448.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>993448.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>962655.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2145653.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2145653.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-98962.45567306643</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2115557</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2115557.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>84.28</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>89.54</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>102.79</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>102.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1396196.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>797567.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>797567.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>869667.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2222751.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2222751.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-209647.8366049416</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1396196</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1396196.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>84.74</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>90.4</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>103.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>103.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>446832.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>676255.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>676255.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>836932.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2237649.02</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2237649.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-283207.9937717296</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>446832</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>446832.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>86.17999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>91.23</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>104.22</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>104.22</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>480517.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>810164.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>810164.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>921369.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2333587.64</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2333587.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-276461.7899467224</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>480517</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>480517.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>87.38000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>91.96</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>105.02</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>105.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>528139.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>854615.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>854615.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1048562.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2414824.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2414824.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-260559.8276986149</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>528139</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>528139.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>89.12</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>92.97</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>105.91</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>105.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1136155.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>931861.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>931861.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1494189.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2699451.5</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2699451.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-233639.3877835108</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1136155</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>90.53999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>93.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>106.84</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>106.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>789636.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>941766.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1903952.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2858383.84</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-251981.9240553796</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>789636</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>789636.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>107.48</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>107.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1116375.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>997608.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>997608.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2034960.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2909917.96</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2909917.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-232059.1571560712</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1116375</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1116375.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>91.28</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>95.66</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>108.04</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>108.04</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>702772.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1032573.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1032573.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2004573.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>3051992.38</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>3051992.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-230317.9845443424</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>702772</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>702772.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>92.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>96.23</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>108.66</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>96.23</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>108.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>914371.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1242510.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1242510.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2031632.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>3137803.82</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>3137803.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-175290.3456510033</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>914371</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>914371.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>91.6</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>92.84</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>90.54</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>92.84</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>90.54000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>34018.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>23269.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>23269.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>25375.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>20196.08</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>20196.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>1302.273244028765</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>34018</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>34018.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>92.14</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>93.08</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>90.52</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>90.52</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>27194.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>20304.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>20304.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>23617.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>19939.46</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>19939.46</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>466.0883970251343</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>27194</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>27194.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>92.4</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>93.21</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>90.52</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>90.52</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>14096.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>21669.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>21669.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>22575.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>19566.56</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>19566.56</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-13.96454144522795</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>14096</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>14096.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>93.32</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>93.34</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>90.49</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>90.48999999999999</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>13827.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>29288.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>29288.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>22115.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>19553.94</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>19553.94</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>704.1014229344364</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>13827</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>13827.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>93.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>93.33</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>90.44</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>90.44</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>27211.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>29946.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>29946.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>22395.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>19406.42</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>19406.42</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1733.584892657724</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>27211</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>27211.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>93.05999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>93.46</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>90.35</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>90.34999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>19195.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>27481.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>27481</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>20789.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>19031.22</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>19031.22</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1708.361817524648</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>19195</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>93.61999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>93.53</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>90.33</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>90.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>34019.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>26929.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>26929.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>19751.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>18957.08</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>18957.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2470.173073851518</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>34019</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>34019.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>94.25999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>93.36</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>90.29</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>90.29000000000001</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>52192.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>23481.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>23481</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>17978.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>18406.26</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>18406.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1881.968687395205</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>52192</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>52192.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>93.9</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>92.75</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>90.13</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>90.13</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>17117.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>14942.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>14942.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>14564.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>17526.18</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>17526.18</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-972.6436035207844</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>17117</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>17117.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>93.94</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>92.31</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>90.04</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>90.04000000000001</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>14882.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>14844.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>14844.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>14755.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>17368.58</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>17368.58</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1257.888176132168</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>14882</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>14882.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>94.05999999999999</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>91.9</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>89.97</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>16437.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>14098.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>14098.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>14361.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>17251.7</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>17251.7</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1380.991559286567</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>16437</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>16437.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN9" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>941766.6</v>
+        <v>931861.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2858383.84</v>
+        <v>2699451.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>94.7</v>
+        <v>93.86</v>
       </c>
       <c r="AN10" t="n">
-        <v>107.48</v>
+        <v>106.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>997608.4</v>
+        <v>941766.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2909917.96</v>
+        <v>2858383.84</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,24 +4641,24 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="BU10" t="inlineStr">
         <is>
           <t>25.44</t>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>95.66</v>
+        <v>94.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>108.04</v>
+        <v>107.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1032573.8</v>
+        <v>997608.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3051992.38</v>
+        <v>2909917.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>96.23</v>
+        <v>95.66</v>
       </c>
       <c r="AN12" t="n">
-        <v>108.66</v>
+        <v>108.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1242510.4</v>
+        <v>1032573.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3137803.82</v>
+        <v>3051992.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-15.33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>92.84</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>90.54000000000001</v>
+        <v>90.53</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-90.81</t>
+          <t>-147.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-93.40</t>
+          <t>-95.17</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34018.0</t>
+          <t>20783.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>23269.2</v>
+        <v>21983.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25375.1</t>
+          <t>25965.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>20196.08</v>
+        <v>20493.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2105</t>
+          <t>-3981</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>556.8364061731578</t>
+          <t>603.8493907358395</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>1302.273244028765</t>
+          <t>862.4208058305885</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>34018.0</t>
+          <t>20783.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>92.14</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>93.08</v>
+        <v>92.84</v>
       </c>
       <c r="AN14" t="n">
-        <v>90.52</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-57.38</t>
+          <t>-90.81</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27194.0</t>
+          <t>34018.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>20304.6</v>
+        <v>23269.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>23617.0</t>
+          <t>25375.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>19939.46</v>
+        <v>20196.08</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3312</t>
+          <t>-2105</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>421.3024356539564</t>
+          <t>556.8364061731578</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>466.0883970251343</t>
+          <t>1302.273244028765</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>27194.0</t>
+          <t>34018.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,37 +6604,37 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,33 +6644,33 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.14</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>93.20999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="AN15" t="n">
         <v>90.52</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-35.13</t>
+          <t>-57.38</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>21669.6</v>
+        <v>20304.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>22575.3</t>
+          <t>23617.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>19566.56</v>
+        <v>19939.46</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-905</t>
+          <t>-3312</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>413.1595335864695</t>
+          <t>421.3024356539564</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-13.96454144522795</t>
+          <t>466.0883970251343</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,17 +7034,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7074,33 +7074,33 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.32</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>93.34</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="AN16" t="n">
-        <v>90.48999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-26.15</t>
+          <t>-35.13</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-89.93</t>
+          <t>-90.74</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>29288.8</v>
+        <v>21669.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22115.8</t>
+          <t>22575.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>19553.94</v>
+        <v>19566.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>-905</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>490.8184563195054</t>
+          <t>413.1595335864695</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>704.1014229344364</t>
+          <t>-13.96454144522795</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,94 +7443,94 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.32</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>93.33</v>
+        <v>93.34</v>
       </c>
       <c r="AN17" t="n">
-        <v>90.44</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-26.15</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-89.27</t>
+          <t>-89.93</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>29946.8</v>
+        <v>29288.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22395.8</t>
+          <t>22115.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>19406.42</v>
+        <v>19553.94</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>452.0397351167907</t>
+          <t>490.8184563195054</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1733.584892657724</t>
+          <t>704.1014229344364</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,94 +7873,94 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.05999999999999</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>93.45999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>90.34999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-21.66</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-89.27</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>27481</v>
+        <v>29946.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>20789.9</t>
+          <t>22395.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>19031.22</v>
+        <v>19406.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>219.0315246548028</t>
+          <t>452.0397351167907</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1708.361817524648</t>
+          <t>1733.584892657724</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8151,17 +8151,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,72 +8208,72 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-3.95</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>93.53</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="AN19" t="n">
-        <v>90.33</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-88.85</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>26929.4</v>
+        <v>27481</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>19751.6</t>
+          <t>20789.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>18957.08</v>
+        <v>19031.22</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-51.75580132153277</t>
+          <t>219.0315246548028</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2470.173073851518</t>
+          <t>1708.361817524648</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,74 +8638,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-8.17</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -8718,14 +8718,14 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>93.36</v>
+        <v>93.53</v>
       </c>
       <c r="AN20" t="n">
-        <v>90.29000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>23481</v>
+        <v>26929.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>18406.26</v>
+        <v>18957.08</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1881.968687395205</t>
+          <t>2470.173073851518</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,92 +9068,92 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-9.15</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-4.14</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>92.75</v>
+        <v>93.36</v>
       </c>
       <c r="AN21" t="n">
-        <v>90.13</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>14942.8</v>
+        <v>23481</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>17526.18</v>
+        <v>18406.26</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-972.6436035207844</t>
+          <t>1881.968687395205</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>92.31</v>
+        <v>92.75</v>
       </c>
       <c r="AN22" t="n">
-        <v>90.04000000000001</v>
+        <v>90.13</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>14844.8</v>
+        <v>14942.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>17368.58</v>
+        <v>17526.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1257.888176132168</t>
+          <t>-972.6436035207844</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,68 +10044,68 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>94.05999999999999</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>91.90000000000001</v>
+        <v>92.31</v>
       </c>
       <c r="AN23" t="n">
-        <v>89.97</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>112994.1652360515</t>
+          <t>112877.28</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>14098.8</v>
+        <v>14844.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14361.0</t>
+          <t>14755.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>17251.7</v>
+        <v>17368.58</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-262</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-882.5122878384688</t>
+          <t>-940.2624244990379</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1380.991559286567</t>
+          <t>-1257.888176132168</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>16437.0</t>
+          <t>14882.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>94.9</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>95.3</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>95.7</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61921.0</t>
+          <t>16328.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.31</v>
+        <v>90.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.05</v>
+        <v>100.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-133.54</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2303736</v>
+        <v>2521164.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1556950.2</t>
+          <t>1598710.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2122460.26</v>
+        <v>2048434.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>746785</t>
+          <t>922454</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-96699.92046831697</t>
+          <t>-49167.48712118959</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>302190.9951926938</t>
+          <t>212260.896288011</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="BU4" t="inlineStr">
         <is>
           <t>25.44</t>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN5" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,161 +4469,161 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN10" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>1205476.457203994</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>931861.8</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2699451.5</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-233639.3877835108</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>1203911.475</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>941766.6</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2858383.84</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-251981.9240553796</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>94.7</v>
+        <v>93.86</v>
       </c>
       <c r="AN11" t="n">
-        <v>107.48</v>
+        <v>106.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>997608.4</v>
+        <v>941766.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2909917.96</v>
+        <v>2858383.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>95.66</v>
+        <v>94.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>108.04</v>
+        <v>107.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1032573.8</v>
+        <v>997608.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3051992.38</v>
+        <v>2909917.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>288.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.33</t>
+          <t>-9.40</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>92.65000000000001</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>90.53</v>
+        <v>90.47</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-147.07</t>
+          <t>-335.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-95.17</t>
+          <t>-97.38</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>20783.0</t>
+          <t>25186.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>21983.6</v>
+        <v>24255.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25965.2</t>
+          <t>26772.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>20493.72</v>
+        <v>20854.02</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3981</t>
+          <t>-2516</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>603.8493907358395</t>
+          <t>643.7477273835715</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>862.4208058305885</t>
+          <t>863.1885789460976</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>20783.0</t>
+          <t>25186.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-15.33</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>92.84</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="AN14" t="n">
-        <v>90.54000000000001</v>
+        <v>90.53</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-90.81</t>
+          <t>-147.07</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-93.40</t>
+          <t>-95.17</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34018.0</t>
+          <t>20783.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>23269.2</v>
+        <v>21983.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25375.1</t>
+          <t>25965.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>20196.08</v>
+        <v>20493.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2105</t>
+          <t>-3981</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>556.8364061731578</t>
+          <t>603.8493907358395</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>1302.273244028765</t>
+          <t>862.4208058305885</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>34018.0</t>
+          <t>20783.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>92.14</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>93.08</v>
+        <v>92.84</v>
       </c>
       <c r="AN15" t="n">
-        <v>90.52</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-57.38</t>
+          <t>-90.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>27194.0</t>
+          <t>34018.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>20304.6</v>
+        <v>23269.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>23617.0</t>
+          <t>25375.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>19939.46</v>
+        <v>20196.08</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-3312</t>
+          <t>-2105</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>421.3024356539564</t>
+          <t>556.8364061731578</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>466.0883970251343</t>
+          <t>1302.273244028765</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>27194.0</t>
+          <t>34018.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,32 +7039,32 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7074,33 +7074,33 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.14</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>93.20999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="AN16" t="n">
         <v>90.52</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-35.13</t>
+          <t>-57.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>21669.6</v>
+        <v>20304.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22575.3</t>
+          <t>23617.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>19566.56</v>
+        <v>19939.46</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-905</t>
+          <t>-3312</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>413.1595335864695</t>
+          <t>421.3024356539564</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-13.96454144522795</t>
+          <t>466.0883970251343</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7504,33 +7504,33 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.32</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>93.34</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="AN17" t="n">
-        <v>90.48999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-26.15</t>
+          <t>-35.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-89.93</t>
+          <t>-90.74</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>29288.8</v>
+        <v>21669.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22115.8</t>
+          <t>22575.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>19553.94</v>
+        <v>19566.56</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>-905</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>490.8184563195054</t>
+          <t>413.1595335864695</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>704.1014229344364</t>
+          <t>-13.96454144522795</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,22 +7873,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.32</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>93.33</v>
+        <v>93.34</v>
       </c>
       <c r="AN18" t="n">
-        <v>90.44</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-26.15</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-89.27</t>
+          <t>-89.93</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>29946.8</v>
+        <v>29288.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22395.8</t>
+          <t>22115.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>19406.42</v>
+        <v>19553.94</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>452.0397351167907</t>
+          <t>490.8184563195054</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1733.584892657724</t>
+          <t>704.1014229344364</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,22 +8303,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.05999999999999</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>93.45999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>90.34999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-21.66</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-89.27</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>27481</v>
+        <v>29946.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>20789.9</t>
+          <t>22395.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>19031.22</v>
+        <v>19406.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>219.0315246548028</t>
+          <t>452.0397351167907</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1708.361817524648</t>
+          <t>1733.584892657724</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,72 +8638,72 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-6.48</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>93.53</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="AN20" t="n">
-        <v>90.33</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-88.85</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>26929.4</v>
+        <v>27481</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>19751.6</t>
+          <t>20789.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>18957.08</v>
+        <v>19031.22</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-51.75580132153277</t>
+          <t>219.0315246548028</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2470.173073851518</t>
+          <t>1708.361817524648</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>34019.0</t>
+          <t>19195.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,74 +9068,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-6.02</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-9.15</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -9148,14 +9148,14 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>93.36</v>
+        <v>93.53</v>
       </c>
       <c r="AN21" t="n">
-        <v>90.29000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>23481</v>
+        <v>26929.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>18406.26</v>
+        <v>18957.08</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1881.968687395205</t>
+          <t>2470.173073851518</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,92 +9498,92 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-11.81</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-5.08</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>92.75</v>
+        <v>93.36</v>
       </c>
       <c r="AN22" t="n">
-        <v>90.13</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>14942.8</v>
+        <v>23481</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>17526.18</v>
+        <v>18406.26</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-972.6436035207844</t>
+          <t>1881.968687395205</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>52.37</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>92.31</v>
+        <v>92.75</v>
       </c>
       <c r="AN23" t="n">
-        <v>90.04000000000001</v>
+        <v>90.13</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-88.22</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>112877.28</t>
+          <t>112770.14978602</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>14844.8</v>
+        <v>14942.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14755.4</t>
+          <t>14564.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>17368.58</v>
+        <v>17526.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>378</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-940.2624244990379</t>
+          <t>-945.2441443485374</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1257.888176132168</t>
+          <t>-972.6436035207844</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>14882.0</t>
+          <t>17117.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16328.0</t>
+          <t>10325.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>62.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>94.28</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.58</v>
+        <v>90.66</v>
       </c>
       <c r="AN2" t="n">
-        <v>100.73</v>
+        <v>100.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.09</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-127.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2521164.8</v>
+        <v>2433421</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1598710.3</t>
+          <t>1615494.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2048434.82</v>
+        <v>2025475.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>922454</t>
+          <t>817926</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-49167.48712118959</t>
+          <t>-26100.81531061689</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>212260.896288011</t>
+          <t>100765.8796475329</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>61921.0</t>
+          <t>16328.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>90.31</v>
+        <v>90.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.05</v>
+        <v>100.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-133.54</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2303736</v>
+        <v>2521164.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1556950.2</t>
+          <t>1598710.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2122460.26</v>
+        <v>2048434.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>746785</t>
+          <t>922454</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-96699.92046831697</t>
+          <t>-49167.48712118959</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>302190.9951926938</t>
+          <t>212260.896288011</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN11" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>941766.6</v>
+        <v>931861.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2858383.84</v>
+        <v>2699451.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>94.7</v>
+        <v>93.86</v>
       </c>
       <c r="AN12" t="n">
-        <v>107.48</v>
+        <v>106.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>997608.4</v>
+        <v>941766.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2909917.96</v>
+        <v>2858383.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>288.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.40</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>92.20999999999999</v>
+        <v>92.09</v>
       </c>
       <c r="AN13" t="n">
-        <v>90.47</v>
+        <v>90.53</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-335.85</t>
+          <t>-925.26</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-97.38</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>25186.0</t>
+          <t>18521.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>24255.4</v>
+        <v>25140.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>26772.1</t>
+          <t>23405.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>20854.02</v>
+        <v>20635.94</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2516</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>643.7477273835715</t>
+          <t>597.3667394250681</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>863.1885789460976</t>
+          <t>342.2713056532994</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>25186.0</t>
+          <t>18521.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>288.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.33</t>
+          <t>-9.40</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>90.44</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>92.65000000000001</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>90.53</v>
+        <v>90.47</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-147.07</t>
+          <t>-335.85</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-95.17</t>
+          <t>-97.38</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>20783.0</t>
+          <t>25186.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>21983.6</v>
+        <v>24255.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25965.2</t>
+          <t>26772.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>20493.72</v>
+        <v>20854.02</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3981</t>
+          <t>-2516</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>603.8493907358395</t>
+          <t>643.7477273835715</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>862.4208058305885</t>
+          <t>863.1885789460976</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>20783.0</t>
+          <t>25186.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-15.33</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.44</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>92.84</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="AN15" t="n">
-        <v>90.54000000000001</v>
+        <v>90.53</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-90.81</t>
+          <t>-147.07</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-93.40</t>
+          <t>-95.17</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34018.0</t>
+          <t>20783.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>23269.2</v>
+        <v>21983.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25375.1</t>
+          <t>25965.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>20196.08</v>
+        <v>20493.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2105</t>
+          <t>-3981</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>556.8364061731578</t>
+          <t>603.8493907358395</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1302.273244028765</t>
+          <t>862.4208058305885</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>34018.0</t>
+          <t>20783.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>92.14</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>93.08</v>
+        <v>92.84</v>
       </c>
       <c r="AN16" t="n">
-        <v>90.52</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-57.38</t>
+          <t>-90.81</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-91.90</t>
+          <t>-93.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>27194.0</t>
+          <t>34018.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>20304.6</v>
+        <v>23269.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>23617.0</t>
+          <t>25375.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>19939.46</v>
+        <v>20196.08</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3312</t>
+          <t>-2105</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>421.3024356539564</t>
+          <t>556.8364061731578</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>466.0883970251343</t>
+          <t>1302.273244028765</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>27194.0</t>
+          <t>34018.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,37 +7464,37 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7504,33 +7504,33 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.14</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>93.20999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="AN17" t="n">
         <v>90.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-35.13</t>
+          <t>-57.38</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>21669.6</v>
+        <v>20304.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22575.3</t>
+          <t>23617.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>19566.56</v>
+        <v>19939.46</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-905</t>
+          <t>-3312</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>413.1595335864695</t>
+          <t>421.3024356539564</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-13.96454144522795</t>
+          <t>466.0883970251343</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,17 +7914,17 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -7934,33 +7934,33 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.32</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>93.34</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="AN18" t="n">
-        <v>90.48999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-26.15</t>
+          <t>-35.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-89.93</t>
+          <t>-90.74</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>29288.8</v>
+        <v>21669.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22115.8</t>
+          <t>22575.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>19553.94</v>
+        <v>19566.56</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>-905</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>490.8184563195054</t>
+          <t>413.1595335864695</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>704.1014229344364</t>
+          <t>-13.96454144522795</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>13827.0</t>
+          <t>14096.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,94 +8303,94 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.32</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>93.33</v>
+        <v>93.34</v>
       </c>
       <c r="AN19" t="n">
-        <v>90.44</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-26.15</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-89.27</t>
+          <t>-89.93</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>29946.8</v>
+        <v>29288.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>22395.8</t>
+          <t>22115.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>19406.42</v>
+        <v>19553.94</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>452.0397351167907</t>
+          <t>490.8184563195054</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1733.584892657724</t>
+          <t>704.1014229344364</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>27211.0</t>
+          <t>13827.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,94 +8733,94 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.05999999999999</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>93.45999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>90.34999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-21.66</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.85</t>
+          <t>-89.27</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>27481</v>
+        <v>29946.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>20789.9</t>
+          <t>22395.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>19031.22</v>
+        <v>19406.42</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>219.0315246548028</t>
+          <t>452.0397351167907</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1708.361817524648</t>
+          <t>1733.584892657724</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>19195.0</t>
+          <t>27211.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,72 +9068,72 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-6.02</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,211 +9184,211 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.61999999999999</t>
+          <t>93.05999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>93.53</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="AN21" t="n">
-        <v>90.33</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-21.66</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-88.85</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>112649.0833333333</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>27481</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>20789.9</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19031.22</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>6691</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>219.0315246548028</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>1708.361817524648</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-88.25</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>112770.14978602</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>34019.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>26929.4</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>19751.6</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18957.08</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>7177</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-51.75580132153277</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>2470.173073851518</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>34019.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BU21" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9466,14 +9466,14 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,74 +9498,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-11.81</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -9578,14 +9578,14 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>55.88</t>
+          <t>49.02</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>94.25999999999999</t>
+          <t>93.61999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>93.36</v>
+        <v>93.53</v>
       </c>
       <c r="AN22" t="n">
-        <v>90.29000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-88.25</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>23481</v>
+        <v>26929.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>17978.6</t>
+          <t>19751.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>18406.26</v>
+        <v>18957.08</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-510.2883240802693</t>
+          <t>-51.75580132153277</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1881.968687395205</t>
+          <t>2470.173073851518</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>52192.0</t>
+          <t>34019.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9896,14 +9896,14 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,92 +9928,92 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-7.69</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30.61</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-7.64</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>55.88</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.25999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>92.75</v>
+        <v>93.36</v>
       </c>
       <c r="AN23" t="n">
-        <v>90.13</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-88.22</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>112770.14978602</t>
+          <t>112649.0833333333</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>14942.8</v>
+        <v>23481</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14564.6</t>
+          <t>17978.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>17526.18</v>
+        <v>18406.26</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-945.2441443485374</t>
+          <t>-510.2883240802693</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-972.6436035207844</t>
+          <t>1881.968687395205</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>17117.0</t>
+          <t>52192.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10325.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.82</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>94.28</t>
+          <t>94.38000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.66</v>
+        <v>90.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>100.32</v>
+        <v>99.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.29</t>
+          <t>-124.63</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2433421</v>
+        <v>2105501</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1615494.4</t>
+          <t>1549474.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2025475.02</v>
+        <v>1998402.46</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>817926</t>
+          <t>556026</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-26100.81531061689</t>
+          <t>-24533.5789539051</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>100765.8796475329</t>
+          <t>-15913.77899199026</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16328.0</t>
+          <t>10325.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>62.88</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>94.28</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>90.58</v>
+        <v>90.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>100.73</v>
+        <v>100.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.09</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-127.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2521164.8</v>
+        <v>2433421</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1598710.3</t>
+          <t>1615494.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2048434.82</v>
+        <v>2025475.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>922454</t>
+          <t>817926</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-49167.48712118959</t>
+          <t>-26100.81531061689</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>212260.896288011</t>
+          <t>100765.8796475329</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>61921.0</t>
+          <t>16328.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>90.31</v>
+        <v>90.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.05</v>
+        <v>100.73</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-133.54</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2303736</v>
+        <v>2521164.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1556950.2</t>
+          <t>1598710.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2122460.26</v>
+        <v>2048434.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>746785</t>
+          <t>922454</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-96699.92046831697</t>
+          <t>-49167.48712118959</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>302190.9951926938</t>
+          <t>212260.896288011</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN12" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>941766.6</v>
+        <v>931861.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2858383.84</v>
+        <v>2699451.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>574.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,211 +5744,211 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>91.14</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-2.93</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>90.23</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-4058.67</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-100.09</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>53457.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>30393</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>25348.8</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>21076.98</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>5044</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>903.8137690069059</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>2589.272431707013</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>53457.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>88.84</t>
-        </is>
-      </c>
-      <c r="AM13" t="n">
-        <v>92.09</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>90.53</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>90.23</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-925.26</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-99.21</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>18521.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>25140.4</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>23405.0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>20635.94</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>597.3667394250681</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>342.2713056532994</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>18521.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>-2.82</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU13" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>288.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-9.40</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,211 +6174,211 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>41.77</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>13.92</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-3.53</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>88.84</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>92.09</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>90.23</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-925.26</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-99.21</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>18521.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>25140.4</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>23405.0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>20635.94</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>597.3667394250681</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>342.2713056532994</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>18521.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-3.25</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>89.3</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>92.20999999999999</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>90.47</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>90.27</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-335.85</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-97.38</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>25186.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>24255.4</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>26772.1</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>20854.02</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-2516</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>643.7477273835715</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>863.1885789460976</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>25186.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>-6.39</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU14" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>288.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.33</t>
+          <t>-9.40</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,211 +6604,211 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-3.15</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>90.27</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-335.85</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-97.38</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>25186.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>24255.4</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>26772.1</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>20854.02</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-2516</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>643.7477273835715</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>863.1885789460976</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>25186.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-6.39</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-2.38</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>90.44</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>92.65000000000001</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>90.53</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>90.34</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-147.07</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-95.17</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>20783.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>21983.6</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>25965.2</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>20493.72</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-3981</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>603.8493907358395</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>862.4208058305885</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>20783.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>-4.12</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU15" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-15.33</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,211 +7034,211 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-2.15</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>90.44</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>90.34</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-147.07</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-95.17</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>20783.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>21983.6</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>25965.2</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>20493.72</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-3981</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>603.8493907358395</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>862.4208058305885</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>20783.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>-4.12</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-2.51</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>92.84</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>90.54000000000001</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>90.36</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-90.81</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-93.40</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>34018.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>23269.2</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>25375.1</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>20196.08</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-2105</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>556.8364061731578</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>1302.273244028765</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>34018.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>-3.25</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU16" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,211 +7464,211 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>92.84</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>90.54000000000001</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>90.36</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-90.81</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-93.40</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>34018.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>23269.2</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>25375.1</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>20196.08</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-2105</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>556.8364061731578</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>1302.273244028765</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34018.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-2.00</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>92.14</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>93.08</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>90.52</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>90.37</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-57.38</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-91.90</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>27194.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>20304.6</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>23617.0</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>19939.46</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>-3312</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>421.3024356539564</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>466.0883970251343</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>27194.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU17" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,37 +7894,37 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>574</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -7934,33 +7934,33 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.14</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>93.20999999999999</v>
+        <v>93.08</v>
       </c>
       <c r="AN18" t="n">
         <v>90.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-35.13</t>
+          <t>-57.38</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-90.74</t>
+          <t>-91.90</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>112649.0833333333</t>
+          <t>112602.9046941679</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>21669.6</v>
+        <v>20304.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22575.3</t>
+          <t>23617.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>19566.56</v>
+        <v>19939.46</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-905</t>
+          <t>-3312</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>413.1595335864695</t>
+          <t>421.3024356539564</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-13.96454144522795</t>
+          <t>466.0883970251343</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14096.0</t>
+          <t>27194.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,211 +8324,211 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>90.52</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>90.38</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-35.13</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-90.74</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>14096.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>21669.6</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>22575.3</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>19566.56</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-905</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>413.1595335864695</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-13.96454144522795</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>14096.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>93.32</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>93.34</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>90.48999999999999</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>90.34</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-26.15</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-89.93</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>13827.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>29288.8</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>22115.8</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>19553.94</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>7173</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>490.8184563195054</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>704.1014229344364</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>13827.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU19" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,232 +8733,232 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>93.32</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>90.34</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-26.15</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-89.93</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>13827.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>29288.8</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>22115.8</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>19553.94</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>490.8184563195054</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>704.1014229344364</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>13827.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>20.67</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
-      <c r="AM20" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>90.44</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>90.33</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-15.61</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-89.27</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>27211.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>29946.8</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>22395.8</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>19406.42</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>7551</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>452.0397351167907</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>1733.584892657724</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>27211.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU20" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,232 +9163,232 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>20.67</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>90.33</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-15.61</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-89.27</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>27211.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>29946.8</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>22395.8</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19406.42</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>7551</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>452.0397351167907</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>1733.584892657724</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>27211.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>93.05999999999999</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>93.45999999999999</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>90.34999999999999</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>90.29</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-21.66</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-88.85</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>19195.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>27481</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>20789.9</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>19031.22</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>6691</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>219.0315246548028</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>1708.361817524648</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>19195.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU21" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>363.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,72 +9498,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-2.12</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>36.34</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,211 +9614,211 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>93.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>90.29</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-21.66</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-88.85</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>27481</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>20789.9</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19031.22</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>6691</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>219.0315246548028</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>1708.361817524648</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>49.02</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-2.16</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>93.61999999999999</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>93.53</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>90.33</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>90.31</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-10.21</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-88.25</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>34019.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>26929.4</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>19751.6</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18957.08</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>7177</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-51.75580132153277</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>2470.173073851518</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>34019.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU22" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>363.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,74 +9928,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>36.34</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-11-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-7.69</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>30.61</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>92.7</t>
@@ -10008,14 +10008,14 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>-5.18</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
       <c r="X23" t="inlineStr">
         <is>
           <t>3.87</t>
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,211 +10044,211 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>49.02</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-2.16</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>93.61999999999999</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>90.33</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>90.31</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-10.21</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>9.94</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-88.25</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>112602.9046941679</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>34019.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>26929.4</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19751.6</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>18957.08</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>7177</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-51.75580132153277</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>2470.173073851518</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>34019.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>智崴</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>8.143300034447124</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>-10.93170756310998</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>1.439593030005594</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>55.88</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>94.25999999999999</t>
-        </is>
-      </c>
-      <c r="AM23" t="n">
-        <v>93.36</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>90.29000000000001</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>90.33</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>8.95</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>9.94</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-87.95</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>112649.0833333333</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>52192.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="n">
-        <v>23481</v>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>17978.6</t>
-        </is>
-      </c>
-      <c r="AZ23" t="n">
-        <v>18406.26</v>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>5502</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-510.2883240802693</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>1881.968687395205</t>
-        </is>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>52192.0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>4.66</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>智崴</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>8.143300034447124</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>-10.93170756310998</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>1.439593030005594</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BU23" t="inlineStr">
         <is>
           <t>5.17</t>
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/垂直應用方案.xlsx
+++ b/Result/checksun_type/垂直應用方案.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>9928.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-22.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,54 +1014,54 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>60.23</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>56.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>94.38000000000001</t>
+          <t>92.98</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.47</v>
+        <v>90.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>99.95</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.63</t>
+          <t>-122.07</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>475957.0</t>
+          <t>914130.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2105501</v>
+        <v>1988974.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1549474.6</t>
+          <t>1588073.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1998402.46</v>
+        <v>1969999.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>556026</t>
+          <t>400901</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-24533.5789539051</t>
+          <t>-30655.90843251303</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-15913.77899199026</t>
+          <t>-64328.72056485666</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>475957.0</t>
+          <t>914130.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10325.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.82</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>94.28</t>
+          <t>94.38000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>90.66</v>
+        <v>90.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>100.32</v>
+        <v>99.95</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.29</t>
+          <t>-124.63</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2433421</v>
+        <v>2105501</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1615494.4</t>
+          <t>1549474.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2025475.02</v>
+        <v>1998402.46</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>817926</t>
+          <t>556026</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-26100.81531061689</t>
+          <t>-24533.5789539051</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>100765.8796475329</t>
+          <t>-15913.77899199026</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16328.0</t>
+          <t>10325.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.82</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>62.88</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>94.28</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>90.58</v>
+        <v>90.66</v>
       </c>
       <c r="AN4" t="n">
-        <v>100.73</v>
+        <v>100.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>104.09</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-127.29</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2521164.8</v>
+        <v>2433421</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1598710.3</t>
+          <t>1615494.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2048434.82</v>
+        <v>2025475.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>922454</t>
+          <t>817926</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-49167.48712118959</t>
+          <t>-26100.81531061689</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>212260.896288011</t>
+          <t>100765.8796475329</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>61921.0</t>
+          <t>16328.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>90.31</v>
+        <v>90.58</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.05</v>
+        <v>100.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-133.54</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2303736</v>
+        <v>2521164.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1556950.2</t>
+          <t>1598710.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2122460.26</v>
+        <v>2048434.82</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>746785</t>
+          <t>922454</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-96699.92046831697</t>
+          <t>-49167.48712118959</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>302190.9951926938</t>
+          <t>212260.896288011</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,221 +2734,221 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>71.02</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>88.17</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-10.63</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>90.68</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>90.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>103.99</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>38.93</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-4.02</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-133.54</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1205341.395596591</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>6063334.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>2303736</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>1556950.2</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2122460.26</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>746785</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-96699.92046831697</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>302190.9951926938</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6063334.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>39.56</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>10.52226299517467</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>27.79118773626352</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-2.044940352257788</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>25.44</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>73.49</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>12.59</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-11.4</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-2.24</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>88.82</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>89.97</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>101.54</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>103.87</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>30.29</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-3.08</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-4.42</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-136.80</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1205105.472972973</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1496761.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>1187172.6</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>1020894.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2058125.44</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>166278</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-169225.5414975917</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-65418.32762892707</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>1496761.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>47.06</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>10.52226299517467</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>27.79118773626352</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-2.044940352257788</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>98.39</t>
-        </is>
-      </c>
       <c r="BW6" t="inlineStr">
         <is>
           <t>15.18%</t>
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN7" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,14 +3361,14 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
       <c r="BU7" t="inlineStr">
         <is>
           <t>25.44</t>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN8" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.02</v>
+        <v